--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno3/anno3_task2_user_chatbot_emotion.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno3/anno3_task2_user_chatbot_emotion.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B33470-0CCA-444F-A10A-454E71742441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34191975-CA10-1A4B-9460-14AB9702B6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="336">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000034-0002</t>
-  </si>
-  <si>
-    <t>Yes, there are some interesting options that I'm considering.</t>
-  </si>
-  <si>
-    <t>But remember to always do your research and be cautious about potential scams or fraudulent investments.</t>
-  </si>
-  <si>
-    <t>But make sure to do your research and understand the risks involved before making any decisions.</t>
-  </si>
-  <si>
-    <t>Just remember that investing always carries some level of risk, so it's important to be cautious and do your research.</t>
-  </si>
-  <si>
-    <t>Just be cautious and do your research before investing in anything.</t>
-  </si>
-  <si>
-    <t>Just make sure to do your research and invest wisely. The market can be unpredictable.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000171-0002</t>
-  </si>
-  <si>
-    <t>Not really. I wanted to try some fancy French cuisine, but couldn't afford it.</t>
-  </si>
-  <si>
-    <t>I'm happy to hear you had a great time exploring the city. What were some of your favorite sights?</t>
-  </si>
-  <si>
-    <t>I loved getting a croissant and coffee every morning. It was the perfect way to start the day.</t>
-  </si>
-  <si>
-    <t>I'm glad you got to experience some of the local culture, and I hope you got to try some delicious French bread at least.</t>
-  </si>
-  <si>
-    <t>I had a great time trying out some of the street food and crepes!</t>
-  </si>
-  <si>
-    <t>But I heard that there are some great local cafes and bakeries in Paris that offer delicious French pastries and sandwiches.</t>
+    <t>SFTANNO-000187-0002</t>
+  </si>
+  <si>
+    <t>I've started using a reusable water bottle instead of constantly buying plastic ones.</t>
+  </si>
+  <si>
+    <t>It's heartbreaking to think about the plastic waste we've already produced. We need to make changes now to prevent further damage.</t>
+  </si>
+  <si>
+    <t>It's really sad that we've reached a point where our daily habits have such a significant impact on the planet.</t>
+  </si>
+  <si>
+    <t>I wish more people would make the effort to reduce their plastic usage. It's a sad reality that we have to fight so hard for something as simple as taking care of our planet.</t>
+  </si>
+  <si>
+    <t>It's sad to think about how much plastic waste we've contributed to in the past. But we can work towards a better future now.</t>
+  </si>
+  <si>
+    <t>It's disheartening to think about how much plastic we waste every day.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000144-0002</t>
+  </si>
+  <si>
+    <t>Did you hear about the recent increase in wildfires due to climate change?</t>
+  </si>
+  <si>
+    <t>It's devastating to think about the impact that climate change is having on our planet and the wildlife that depends on it.</t>
+  </si>
+  <si>
+    <t>It's so sad to think about the devastating impact climate change is having on our planet.</t>
+  </si>
+  <si>
+    <t>It's heartbreaking to think about the loss of so many homes and lives due to these devastating wildfires.</t>
+  </si>
+  <si>
+    <t>It's sad to think about the impact that wildfires can have on wildlife and habitats.</t>
+  </si>
+  <si>
+    <t>It's so sad to see how much damage is being done to our environment.</t>
   </si>
   <si>
     <t>SFTANNO-000025-0002</t>
@@ -119,508 +119,508 @@
     <t>I'm surprised at how much better you're feeling about the situation.</t>
   </si>
   <si>
-    <t>SFTANNO-000007-0002</t>
-  </si>
-  <si>
-    <t>They actually offered me the job!</t>
-  </si>
-  <si>
-    <t>Are you feeling overwhelmed by the new opportunity?</t>
-  </si>
-  <si>
-    <t>Wow, congratulations! What are your initial thoughts about the new job?</t>
-  </si>
-  <si>
-    <t>I'm happy for you, but now you have to think about the new job and the responsibilities that come with it.</t>
-  </si>
-  <si>
-    <t>Congratulations, but now comes the hard part: deciding if it's the right fit for you.</t>
-  </si>
-  <si>
-    <t>It's great news, but also scary, right?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000084-0002</t>
-  </si>
-  <si>
-    <t>My coach just retired, and I feel like I've lost a mentor.</t>
-  </si>
-  <si>
-    <t>But also, think of all the new opportunities and growth that lie ahead with a new coach.</t>
-  </si>
-  <si>
-    <t>But remember, you'll always have the skills and knowledge they taught you.</t>
-  </si>
-  <si>
-    <t>But don't let that fear hold you back from reaching out to the new coach and asking for guidance.</t>
-  </si>
-  <si>
-    <t>But remember, you have the skills and experience to continue growing as an athlete.</t>
-  </si>
-  <si>
-    <t>But don't worry, you can still find guidance and support from other sources, like your teammates and other coaches.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000156-0002</t>
-  </si>
-  <si>
-    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
-  </si>
-  <si>
-    <t>I'm still a bit nervous about making changes, but I'm willing to try.</t>
-  </si>
-  <si>
-    <t>But I'm still a bit afraid to make any changes. What if I mess up?</t>
-  </si>
-  <si>
-    <t>But I'm still a bit afraid of making too many changes at once.</t>
-  </si>
-  <si>
-    <t>I'm just a bit nervous about messing up and not doing it right.</t>
-  </si>
-  <si>
-    <t>But I'm worried about keeping plants alive. Do you have any tips?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000167-0002</t>
-  </si>
-  <si>
-    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
-  </si>
-  <si>
-    <t>I'm happy to see that AI can help us in our daily lives, like in our homes or even in our cars.</t>
-  </si>
-  <si>
-    <t>I'm thrilled to think about the possibilities that AI could bring to our daily lives, making them easier and more efficient.</t>
-  </si>
-  <si>
-    <t>I'm excited to see how AI will improve our daily lives and make things more efficient.</t>
-  </si>
-  <si>
-    <t>It's exciting to think about the possibilities and advancements that AI will bring to our daily lives.</t>
-  </si>
-  <si>
-    <t>I'm excited to see how AI can help us streamline our daily routines and make things more efficient.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000000-0002</t>
-  </si>
-  <si>
-    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
-  </si>
-  <si>
-    <t>That's understandable. How do you think the story will go on without them?</t>
-  </si>
-  <si>
-    <t>I understand how you feel. How did you cope with that loss?</t>
-  </si>
-  <si>
-    <t>It's definitely a bummer when that happens. Have you considered skipping the next book?</t>
-  </si>
-  <si>
-    <t>It's tough when a favorite character dies. How are you coping with it?</t>
-  </si>
-  <si>
-    <t>It can be disappointing when a beloved character is taken away. How did you react?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000182-0002</t>
-  </si>
-  <si>
-    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
-  </si>
-  <si>
-    <t>It's a heavy topic, but understanding history is crucial for a better future.</t>
-  </si>
-  <si>
-    <t>Yes, understanding the past can help us avoid making the same mistakes in the future.</t>
-  </si>
-  <si>
-    <t>I agree, it's crucial to learn from history and its darker aspects.</t>
-  </si>
-  <si>
-    <t>It's a difficult subject, but important to understand.</t>
-  </si>
-  <si>
-    <t>It's a difficult but important period of history to learn about.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000004-0002</t>
-  </si>
-  <si>
-    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
-  </si>
-  <si>
-    <t>Have you considered taking him for an eye exam?</t>
-  </si>
-  <si>
-    <t>Maybe it's a good idea to schedule an appointment with an eye doctor.</t>
-  </si>
-  <si>
-    <t>I'm sure it's just a precautionary measure, but it's always better to be safe than sorry.</t>
-  </si>
-  <si>
-    <t>Have you considered taking him to an optometrist to get his eyes checked?</t>
-  </si>
-  <si>
-    <t>It's important to have him checked by an eye doctor as soon as possible.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000160-0002</t>
-  </si>
-  <si>
-    <t>Did you hear about that controversial moment at the awards show?</t>
-  </si>
-  <si>
-    <t>It's shocking how some people can't control their emotions in public.</t>
-  </si>
-  <si>
-    <t>It's shocking that someone could be so disrespectful in that setting.</t>
-  </si>
-  <si>
-    <t>I can't believe how some people still think that way.</t>
-  </si>
-  <si>
-    <t>I'm surprised they thought that would be acceptable to air on live TV.</t>
-  </si>
-  <si>
-    <t>I can't believe they let that happen in the first place.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000165-0002</t>
-  </si>
-  <si>
-    <t>I just heard about a close friend moving to a different country, and I'm really going to miss them.</t>
-  </si>
-  <si>
-    <t>But at the same time, you'll have new experiences and memories to create that you never would have had if you didn't move away.</t>
-  </si>
-  <si>
-    <t>But remember that they're just moving to a different country, not to another planet. It's not like you'll never see them again.</t>
-  </si>
-  <si>
-    <t>But it's also an exciting opportunity for them to explore new places and experiences.</t>
-  </si>
-  <si>
-    <t>But there's also excitement in new beginnings and the possibility of future adventures together.</t>
-  </si>
-  <si>
-    <t>But remember, even though they're far away, you can still stay connected through technology and visit them when you can.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000190-0002</t>
-  </si>
-  <si>
-    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
-  </si>
-  <si>
-    <t>It's great to lose yourself in a good show. Have you discovered any new favorites lately?</t>
-  </si>
-  <si>
-    <t>But at the same time, it's a great way to escape reality for a while.</t>
-  </si>
-  <si>
-    <t>I understand your fear, but you've discovered some great shows!</t>
-  </si>
-  <si>
-    <t>Don't worry; it happens to the best of us. How do you usually manage your time when binge-watching?</t>
-  </si>
-  <si>
-    <t>It's great that you're aware of it. Maybe you can try setting limits or taking breaks.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000053-0002</t>
-  </si>
-  <si>
-    <t>I just found out that my friend's band is performing at a local venue tomorrow night.</t>
-  </si>
-  <si>
-    <t>That's such great news! You'll have a fantastic time at the show.</t>
-  </si>
-  <si>
-    <t>I'm so happy for you, supporting local music is always a great experience.</t>
-  </si>
-  <si>
-    <t>That sounds like such a fun night out! I hope you have a great time at the show!</t>
-  </si>
-  <si>
-    <t>I'm so excited to hear them play live! Let's go check it out.</t>
-  </si>
-  <si>
-    <t>That's so exciting, I hope you have a great time!</t>
-  </si>
-  <si>
-    <t>SFTANNO-000067-0002</t>
-  </si>
-  <si>
-    <t>I've tried, but there are so many sources out there with conflicting information that they trust the ones that align with their beliefs.</t>
-  </si>
-  <si>
-    <t>It's frustrating that some people refuse to consider the consequences of their actions and the potential harm they could cause to others.</t>
-  </si>
-  <si>
-    <t>It's disgusting that people can choose to believe whatever they want, even if it's not true, and put others' health at risk.</t>
-  </si>
-  <si>
-    <t>It's disgusting that people are willing to risk their health and others by refusing to vaccinate themselves and their children.</t>
-  </si>
-  <si>
-    <t>It's truly disgusting that people can easily fall for misinformation about vaccines, and it can have serious consequences for public health.</t>
-  </si>
-  <si>
-    <t>It's disgusting that some people prioritize their own beliefs over the health and safety of others.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000141-0002</t>
-  </si>
-  <si>
-    <t>I hope so, as long as it's used for ethical purposes.</t>
-  </si>
-  <si>
-    <t>It's a double-edged sword, with great potential for good, but also the risk of misuse.</t>
-  </si>
-  <si>
-    <t>It's definitely a technology that has the potential to be used for good or bad.</t>
-  </si>
-  <si>
-    <t>It's a double-edged sword, it has the potential to do a lot of good, but also a lot of harm.</t>
-  </si>
-  <si>
-    <t>Do you think there will ever be a point where VR is as common as regular video games?</t>
-  </si>
-  <si>
-    <t>Have you heard of any recent developments in VR technology?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000169-0002</t>
-  </si>
-  <si>
-    <t>Companies need to be held accountable for their security measures, and regulations need to be put in place to ensure that they are.</t>
-  </si>
-  <si>
-    <t>It might be helpful to look into how other countries regulate 5G security and see if there are any best practices that we can adopt.</t>
-  </si>
-  <si>
-    <t>It's important to keep the conversation going and advocate for better security measures.</t>
-  </si>
-  <si>
-    <t>It's a complex issue, but regulations can help ensure companies prioritize security alongside profit.</t>
-  </si>
-  <si>
-    <t>It's important to hold companies accountable for their security measures, and regulations could be a good way to ensure that they are taking proper measures.</t>
-  </si>
-  <si>
-    <t>It's important to have a balance between regulations and innovation to ensure that security measures are effective.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000001-0002</t>
-  </si>
-  <si>
-    <t>I finished that book you recommended, and it was amazing!</t>
-  </si>
-  <si>
-    <t>I hope I don't jinx it, but I'm a bit nervous about recommending another book to you.</t>
-  </si>
-  <si>
-    <t>I'm happy you liked it, but I'm a bit scared of not finding other books that you'll enjoy. What did you like about it?</t>
-  </si>
-  <si>
-    <t>I'm so happy you enjoyed it! However, I'm a bit afraid that my other recommendations won't live up to that one.</t>
-  </si>
-  <si>
-    <t>Now, what book should I recommend next? I'm afraid I'll disappoint you with my choice.</t>
-  </si>
-  <si>
-    <t>I'm thrilled to hear that, but I hope I haven't spoiled anything for you.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000161-0002</t>
-  </si>
-  <si>
-    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
-  </si>
-  <si>
-    <t>It's unacceptable. They need to be held accountable for their actions and be more transparent with their employees.</t>
-  </si>
-  <si>
-    <t>They should be held accountable for the way they handled this situation. It's completely unprofessional.</t>
-  </si>
-  <si>
-    <t>It's infuriating how they handled this. They should have been more open and considerate of their employees' feelings.</t>
-  </si>
-  <si>
-    <t>It's infuriating that they would treat their employees like this. We deserve better than this.</t>
-  </si>
-  <si>
-    <t>I'm angry that they would treat their employees this way. They should be held accountable for their actions.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000013-0002</t>
-  </si>
-  <si>
-    <t>I've never really thought about it, but I'm interested in exploring more.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that ballet is often overlooked and underappreciated in our culture, but I'm glad you're interested in exploring it more.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that ballet is often seen as elitist or only for a certain type of person, but it's really for everyone to enjoy.</t>
-  </si>
-  <si>
-    <t>Although I do think some ballets can be overly pretentious and snobbish, there are so many beautiful and unique stories that are worth exploring.</t>
-  </si>
-  <si>
-    <t>Although there are so many beautiful ballets out there, it's unfortunate that the industry can be so limiting and exclusive.</t>
-  </si>
-  <si>
-    <t>It's a shame that there's still a lot of stigma and misconceptions surrounding ballet, but I hope you find some beautiful performances that change your mind.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000155-0002</t>
-  </si>
-  <si>
-    <t>Not really. I'm not really that handy.</t>
-  </si>
-  <si>
-    <t>It's not fair that you have to make these changes. You shouldn't have to do all the work.</t>
-  </si>
-  <si>
-    <t>It's frustrating when you don't have the skills to make those changes. Have you considered hiring a professional?</t>
-  </si>
-  <si>
-    <t>It's not fair that you have to spend so much money and time on something that should be a happy inheritance.</t>
-  </si>
-  <si>
-    <t>It's ridiculous that we have to spend so much money to make everything work together.</t>
-  </si>
-  <si>
-    <t>It's frustrating that the furniture doesn't fit your style, but don't worry, we'll find a solution.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000055-0002</t>
-  </si>
-  <si>
-    <t>I really like the rhythm of the drums in African music.</t>
-  </si>
-  <si>
-    <t>I'm so happy to hear that you like African music, it's such a unique and exciting genre!</t>
-  </si>
-  <si>
-    <t>I feel so happy when I listen to African music because it always makes me want to dance.</t>
-  </si>
-  <si>
-    <t>African music is so diverse and rich in rhythm, it's always a joy to listen to.</t>
-  </si>
-  <si>
-    <t>I'm excited to explore African music now, I bet it has some great rhythms to dance to.</t>
-  </si>
-  <si>
-    <t>I love learning about different cultures and their music.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000099-0002</t>
-  </si>
-  <si>
-    <t>I have, but it still feels like such a big cost.</t>
-  </si>
-  <si>
-    <t>It's a lot of money to spend on a console, I worry about the long-term investment.</t>
-  </si>
-  <si>
-    <t>It's scary to think about spending so much money on a console, but the new games are so exciting.</t>
-  </si>
-  <si>
-    <t>I'm afraid I won't be able to afford it, but I hope to be able to soon.</t>
-  </si>
-  <si>
-    <t>It's tough to decide whether it's worth the investment.</t>
-  </si>
-  <si>
-    <t>I'm worried about the cost of games as well, it adds up quickly.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000002-0002</t>
-  </si>
-  <si>
-    <t>Not yet, everything is still uncertain due to the pandemic.</t>
-  </si>
-  <si>
-    <t>It's frustrating that the pandemic has caused so much uncertainty and loss in the industry.</t>
-  </si>
-  <si>
-    <t>It's frustrating how the pandemic has affected so many aspects of our lives, especially for those in creative fields.</t>
-  </si>
-  <si>
-    <t>It's frustrating how much the pandemic has disrupted the book industry and author events.</t>
-  </si>
-  <si>
-    <t>It's frustrating that the pandemic is still affecting so many aspects of our lives. I hope things get better soon.</t>
-  </si>
-  <si>
-    <t>It's frustrating that the pandemic is still affecting the industry. But I'm sure your book will still find its way to readers.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000149-0002</t>
-  </si>
-  <si>
-    <t>Certain personality types are often dismissed or overlooked in creative industries.</t>
-  </si>
-  <si>
-    <t>It's maddening that creativity is still so narrowly defined by personality types. We need to break down those stereotypes.</t>
-  </si>
-  <si>
-    <t>It's frustrating that certain personality types are still overlooked and underrepresented in creative fields. We need to work towards a more inclusive industry.</t>
-  </si>
-  <si>
-    <t>It's infuriating that certain personalities are not given the same opportunities in creative industries. We need to work towards a more inclusive and diverse industry.</t>
-  </si>
-  <si>
-    <t>It's unacceptable that certain personality types are often overlooked or dismissed in the creative industry. We need to continue to push for inclusivity and representation.</t>
-  </si>
-  <si>
-    <t>It's unacceptable how certain personality types are overlooked and not given equal opportunities.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000070-0002</t>
-  </si>
-  <si>
-    <t>Have you heard about the recent discovery of gravitational waves?</t>
-  </si>
-  <si>
-    <t>I can't believe how much we still have to learn about the universe.</t>
-  </si>
-  <si>
-    <t>That's amazing! I can't believe we can detect such a faint signal from across the universe.</t>
-  </si>
-  <si>
-    <t>That's incredible! I didn't even realize it was possible to detect gravitational waves.</t>
-  </si>
-  <si>
-    <t>That's amazing! I didn't even know that was possible.</t>
-  </si>
-  <si>
-    <t>I'm surprised you're not more excited about it.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000176-0002</t>
-  </si>
-  <si>
-    <t>No, just a pot for the pasta and a pan for the sauce.</t>
-  </si>
-  <si>
-    <t>Great, I'm ready to give it a try.</t>
-  </si>
-  <si>
-    <t>Let me know how it turns out! I'm happy to help if you need any guidance.</t>
-  </si>
-  <si>
-    <t>Let's begin by boiling the pasta, and then we can make the sauce.</t>
-  </si>
-  <si>
-    <t>Sounds like a perfect recipe for a beginner. I'm excited to try it out.</t>
-  </si>
-  <si>
-    <t>Sounds like a great meal. I'm excited to hear how it turns out.</t>
+    <t>SFTANNO-000103-0002</t>
+  </si>
+  <si>
+    <t>I've been browsing, but I don't want to compromise on quality either.</t>
+  </si>
+  <si>
+    <t>It's tough when you can't find the right fit, but keep looking and don't settle for less.</t>
+  </si>
+  <si>
+    <t>It's a tough balance between finding something within budget and not sacrificing quality.</t>
+  </si>
+  <si>
+    <t>It's important to prioritize quality, especially for something like a VR headset.</t>
+  </si>
+  <si>
+    <t>It's tough to find the right balance, but I'm sure you'll find something that works for you.</t>
+  </si>
+  <si>
+    <t>It's tough when we want to invest in new technology, but have to be mindful of our budget.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000191-0002</t>
+  </si>
+  <si>
+    <t>I don't have the budget for that.</t>
+  </si>
+  <si>
+    <t>Don't worry; there are many online tutorials that can help you learn how to do it yourself and save money.</t>
+  </si>
+  <si>
+    <t>That's okay, sometimes a fresh coat of paint can make a big difference! There are many affordable ways to update your furniture.</t>
+  </si>
+  <si>
+    <t>There are many free tutorials online that can help you learn how to refinish furniture.</t>
+  </si>
+  <si>
+    <t>I'm happy to help you brainstorm some budget-friendly options for refinishing your furniture.</t>
+  </si>
+  <si>
+    <t>But you can still learn new DIY skills and try different projects that are within your budget.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000094-0002</t>
+  </si>
+  <si>
+    <t>Actually, I always opt for middle seats. Fewer distractions around me.</t>
+  </si>
+  <si>
+    <t>I can't imagine sitting in the middle seat, it just sounds uncomfortable.</t>
+  </si>
+  <si>
+    <t>The middle seat is the worst; you're stuck in the middle of everything and can't even stretch out.</t>
+  </si>
+  <si>
+    <t>That's interesting, but I'm not sure I could handle sitting in the middle with people on either side of me.</t>
+  </si>
+  <si>
+    <t>I can't believe you choose the middle seat. I would never want to be stuck in the middle.</t>
+  </si>
+  <si>
+    <t>I'm surprised that you prefer middle seats; I always find them cramped and uncomfortable.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000064-0002</t>
+  </si>
+  <si>
+    <t>I think we should reach out to local organizations and get involved in promoting change.</t>
+  </si>
+  <si>
+    <t>It's unacceptable that these issues are still going unchecked. It's time for us to be proactive and show our advocates for our beliefs.</t>
+  </si>
+  <si>
+    <t>It's unacceptable that we still have to fight for basic rights and equality. It's time to take action and create change.</t>
+  </si>
+  <si>
+    <t>It's unacceptable that some people still see certain issues as acceptable. We need to keep pushing for change until we get the results we want.</t>
+  </si>
+  <si>
+    <t>It's frustrating that certain issues still persist, but we can work together to create change and make a difference.</t>
+  </si>
+  <si>
+    <t>It's unacceptable that certain issues are still being overlooked and not given the attention they deserve. We need to be more vocal and take action to create change.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000159-0002</t>
+  </si>
+  <si>
+    <t>We should start by setting some ground rules for respectful discussion.</t>
+  </si>
+  <si>
+    <t>I'm happy we're taking this step towards better communication.</t>
+  </si>
+  <si>
+    <t>I'm happy we can start fresh with clear boundaries.</t>
+  </si>
+  <si>
+    <t>I'm happy we're taking steps towards a healthier conversation.</t>
+  </si>
+  <si>
+    <t>I'm happy we're taking steps towards a better conversation.</t>
+  </si>
+  <si>
+    <t>I'm happy we're working towards a healthier conversation.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000107-0002</t>
+  </si>
+  <si>
+    <t>It's so cloudy out, I don't even want to leave my house.</t>
+  </si>
+  <si>
+    <t>Did you know that rain can actually be good for your mood? It's been proven to increase the production of serotonin in your brain.</t>
+  </si>
+  <si>
+    <t>Have you tried going for a walk in the rain? It can be really refreshing!</t>
+  </si>
+  <si>
+    <t>I'm surprised you're feeling so down, you're usually so optimistic!</t>
+  </si>
+  <si>
+    <t>Have you ever tried going for a walk in the rain? It can be really peaceful.</t>
+  </si>
+  <si>
+    <t>Did you know that some people find cloudy days calming and peaceful?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000152-0002</t>
+  </si>
+  <si>
+    <t>I'm worried I won't be able to make anything as beautiful as the examples I've seen.</t>
+  </si>
+  <si>
+    <t>It's frustrating that the scrapbooking industry can be so competitive and cutthroat.</t>
+  </si>
+  <si>
+    <t>It's ridiculous that some people expect perfection right away.</t>
+  </si>
+  <si>
+    <t>It's frustrating that the industry can make it seem like only perfection is acceptable.</t>
+  </si>
+  <si>
+    <t>It's ridiculous that people can be so judgmental and critical.</t>
+  </si>
+  <si>
+    <t>It's infuriating how much pressure society puts on people to create perfect crafts.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000075-0002</t>
+  </si>
+  <si>
+    <t>This lab is such a mess! They don't even have the right equipment!</t>
+  </si>
+  <si>
+    <t>It's important to make sure that we follow all safety protocols and procedures to avoid any accidents or injuries.</t>
+  </si>
+  <si>
+    <t>I'm worried that the lack of equipment could put our safety at risk in the lab.</t>
+  </si>
+  <si>
+    <t>I'm worried that we might not be able to complete the experiment as planned because of the equipment shortage.</t>
+  </si>
+  <si>
+    <t>It's important to make sure we're following all safety protocols and using the correct equipment to avoid any accidents or injuries.</t>
+  </si>
+  <si>
+    <t>It's scary to think about the potential safety hazards and consequences of not having the proper equipment.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000040-0002</t>
+  </si>
+  <si>
+    <t>Yes, please. Thank you.</t>
+  </si>
+  <si>
+    <t>It's a shame that so many people have to deal with credit card debt, but I'm glad I can help you find some resources to get back on track.</t>
+  </si>
+  <si>
+    <t>It's so unfortunate that so many people are struggling with credit card debt.</t>
+  </si>
+  <si>
+    <t>It's so frustrating when credit card companies make it difficult for people to manage their debt.</t>
+  </si>
+  <si>
+    <t>It's frustrating that credit card companies make it so easy to get into debt. But, it's important to remember that there are ways to get out of it and start fresh.</t>
+  </si>
+  <si>
+    <t>It's disgusting how credit card companies take advantage of people's financial struggles. It's important to stay informed and protect yourself.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000096-0002</t>
+  </si>
+  <si>
+    <t>I missed the last train, and I'm stuck in the city.</t>
+  </si>
+  <si>
+    <t>I'm sorry you're stuck here alone. Do you need help getting a ride or anything?</t>
+  </si>
+  <si>
+    <t>I'm sorry you're in that position. Is there a hotel nearby that you could stay at for the night?</t>
+  </si>
+  <si>
+    <t>I'm so sorry, it's a terrible feeling being stranded like that.</t>
+  </si>
+  <si>
+    <t>It's tough to be in that situation, but we can help you find a safe place to stay.</t>
+  </si>
+  <si>
+    <t>It's tough when things like this happen, but we'll figure it out.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000158-0002</t>
+  </si>
+  <si>
+    <t>They've been seeing someone else behind my back!</t>
+  </si>
+  <si>
+    <t>It's infuriating how they could do that to you.</t>
+  </si>
+  <si>
+    <t>I'm so angry for you. How could they do that?</t>
+  </si>
+  <si>
+    <t>That's unacceptable! They don't deserve you.</t>
+  </si>
+  <si>
+    <t>How could they do this to you? It's infuriating!</t>
+  </si>
+  <si>
+    <t>I can't believe they would do that to you. It's infuriating.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000177-0002</t>
+  </si>
+  <si>
+    <t>I can't stand the smell of fried food, but I love the taste. Is there a way to avoid the smell but still get the crispy texture?</t>
+  </si>
+  <si>
+    <t>It's a common issue, but hopefully, my tip can help you enjoy the taste of fried food without the smell.</t>
+  </si>
+  <si>
+    <t>I know how unpleasant the smell can be, hopefully, these methods can help you enjoy the taste without the odor.</t>
+  </si>
+  <si>
+    <t>I completely understand how much you dislike the smell of fried food, but it's great that you still enjoy the taste.</t>
+  </si>
+  <si>
+    <t>I completely understand, the smell of fried food can be overwhelming, but hopefully, my tips can help you still enjoy the taste.</t>
+  </si>
+  <si>
+    <t>I completely understand how unpleasant the smell can be, but it's worth it for the delicious taste.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000045-0002</t>
+  </si>
+  <si>
+    <t>Yes, I found some really tasty vegetarian tacos at a local Mexican restaurant.</t>
+  </si>
+  <si>
+    <t>It's interesting to hear about your experiences, but I'm not sure I could ever give up meat completely.</t>
+  </si>
+  <si>
+    <t>Maybe I should give them a try sometime.</t>
+  </si>
+  <si>
+    <t>It's okay to have different preferences, and I'm glad you found something you enjoyed.</t>
+  </si>
+  <si>
+    <t>It's always interesting to try new things, but I'm definitely a meat-lover at heart.</t>
+  </si>
+  <si>
+    <t>It's always good to have more options for people who choose to be vegetarian.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000143-0002</t>
+  </si>
+  <si>
+    <t>Why is there such a gender gap in the tech industry? It's infuriating.</t>
+  </si>
+  <si>
+    <t>It's disgusting that some companies even have policies in place to discourage women from joining.</t>
+  </si>
+  <si>
+    <t>It's disgusting that women have to work so hard to be taken seriously in the industry.</t>
+  </si>
+  <si>
+    <t>It's disappointing that women are still underrepresented and have to work so much harder to prove themselves.</t>
+  </si>
+  <si>
+    <t>And it's disgusting how women are often treated in the industry, with lower pay and fewer opportunities.</t>
+  </si>
+  <si>
+    <t>It's disgusting how women are still being paid less and passed over for promotions.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000145-0002</t>
+  </si>
+  <si>
+    <t>That's a great idea! I hadn't thought about that.</t>
+  </si>
+  <si>
+    <t>Yes, let's work together to make a positive impact on our planet!</t>
+  </si>
+  <si>
+    <t>That's the spirit! Keep up the great work and we can make a difference together.</t>
+  </si>
+  <si>
+    <t>I'm so happy to hear that! It's so important to find resources and support for making these changes.</t>
+  </si>
+  <si>
+    <t>It's so inspiring to see people taking action and making a positive impact. Keep up the great work!</t>
+  </si>
+  <si>
+    <t>It's great to see you taking steps towards sustainability! I'm excited to see what changes you'll make next.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000089-0002</t>
+  </si>
+  <si>
+    <t>They have a really solid defense and excellent ball control.</t>
+  </si>
+  <si>
+    <t>It's too bad when a team's strengths can also be their downfall.</t>
+  </si>
+  <si>
+    <t>It's too bad that not everyone has the same opportunities to play or even watch soccer.</t>
+  </si>
+  <si>
+    <t>It's hard to watch a team like that and not feel sad about your own team's performance.</t>
+  </si>
+  <si>
+    <t>It's too bad that some teams can't seem to compete with them, it's not very exciting.</t>
+  </si>
+  <si>
+    <t>It's a shame they don't have as much support as other teams, they deserve more recognition.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000132-0002</t>
+  </si>
+  <si>
+    <t>I'm considering an adventure trip to Patagonia.</t>
+  </si>
+  <si>
+    <t>Patagonia's natural wonders are breathtaking. I'm surprised you're thinking of going there.</t>
+  </si>
+  <si>
+    <t>That's a surprising and exciting choice! Patagonia offers breathtaking landscapes.</t>
+  </si>
+  <si>
+    <t>Patagonia is a dream destination for many, and I'm excited for you!</t>
+  </si>
+  <si>
+    <t>It's awe-inspiring, but remember to prepare well for such an adventure.</t>
+  </si>
+  <si>
+    <t>Patagonia is a unique destination with breathtaking landscapes. I'm surprised you're going there!</t>
+  </si>
+  <si>
+    <t>SFTANNO-000051-0002</t>
+  </si>
+  <si>
+    <t>I'm nervous about presenting my film at the festival. What if it's not good enough?</t>
+  </si>
+  <si>
+    <t>And if it doesn't go as planned, remember that failure is a part of the process and it's okay to learn from it.</t>
+  </si>
+  <si>
+    <t>It's a tough industry, but you should be proud of your work. Remember to take care of yourself and not let the negativity get to you.</t>
+  </si>
+  <si>
+    <t>It's tough, but don't let fear hold you back. Your work is worth sharing and showing the world.</t>
+  </si>
+  <si>
+    <t>I know it's tough, but remember that you made something amazing, and that's something to be proud of.</t>
+  </si>
+  <si>
+    <t>It's tough, but you have to remember that every filmmaker goes through that same fear. Just trust in your vision.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000181-0002</t>
+  </si>
+  <si>
+    <t>Sanctions could continue to be an effective tool, but it will take more international cooperation to bring about a peaceful solution.</t>
+  </si>
+  <si>
+    <t>Agreed, it will require a lot of diplomacy and coordination to bring about a resolution.</t>
+  </si>
+  <si>
+    <t>It's a delicate situation, and it will require a multifaceted approach to bring about a peaceful resolution.</t>
+  </si>
+  <si>
+    <t>Yes, and it's crucial that the international community works together to find a peaceful solution.</t>
+  </si>
+  <si>
+    <t>I agree, and I hope that we can work together to bring about a peaceful resolution to this crisis.</t>
+  </si>
+  <si>
+    <t>Yes, it's essential to have a unified front in dealing with Russia.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000137-0002</t>
+  </si>
+  <si>
+    <t>I haven't, but I'm thinking of it. Although the thought of traveling alone terrifies me.</t>
+  </si>
+  <si>
+    <t>I've traveled alone, and it was one of the most liberating experiences of my life. You'll have the freedom to do what you want and go where you want.</t>
+  </si>
+  <si>
+    <t>I've had the most incredible experiences traveling solo. It's amazing to be able to explore at your own pace and meet new people.</t>
+  </si>
+  <si>
+    <t>But, I'm excited for you to try it! Traveling alone can be an incredible experience, and you might discover new things about yourself.</t>
+  </si>
+  <si>
+    <t>I traveled solo to Italy, and it was one of the happiest experiences of my life. I met amazing people, tried new things, and learned so much about myself.</t>
+  </si>
+  <si>
+    <t>Solo travel can be life-changing. You have the freedom to do whatever you want and meet new people.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000163-0002</t>
+  </si>
+  <si>
+    <t>I wish I could go back in time to see history up close.</t>
+  </si>
+  <si>
+    <t>It's a common feeling, but we should be grateful for the ability to learn about history through books and documentaries.</t>
+  </si>
+  <si>
+    <t>While I understand your longing, it's essential to remember that time travel is just a fantasy.</t>
+  </si>
+  <si>
+    <t>We can learn a lot about history through books and documentaries.</t>
+  </si>
+  <si>
+    <t>We can always learn about history through research and study.</t>
+  </si>
+  <si>
+    <t>Maybe there's a way to experience history without time travel, like visiting museums or historical sites.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000134-0002</t>
+  </si>
+  <si>
+    <t>I'm considering visiting Tulum in Mexico.</t>
+  </si>
+  <si>
+    <t>It's important to do research on the local businesses and ensure they are ethical and sustainable.</t>
+  </si>
+  <si>
+    <t>It's unfortunate that some tour companies prioritize profit over sustainability and have a negative impact on the environment.</t>
+  </si>
+  <si>
+    <t>Be careful of the over-tourism and pollution in some areas, but it's still a beautiful and unique place to visit.</t>
+  </si>
+  <si>
+    <t>Just be cautious and do your research to avoid any unsavory or unsafe situations.</t>
+  </si>
+  <si>
+    <t>However, I've heard that there are some issues with pollution and overcrowding in that area.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000091-0002</t>
+  </si>
+  <si>
+    <t>I'm looking to invest in a new bike. Do you have any recommendations?</t>
+  </si>
+  <si>
+    <t>I recently discovered a great local bike shop that offers customized bikes, it might be worth checking out.</t>
+  </si>
+  <si>
+    <t>I was just reading about this new bike brand that has some great reviews. Have you heard of it?</t>
+  </si>
+  <si>
+    <t>Really? I've heard they're great for long rides. Have you looked into any specific models?</t>
+  </si>
+  <si>
+    <t>I didn't expect you to be interested in bikes, but I'd be happy to share my recommendation.</t>
+  </si>
+  <si>
+    <t>I'm surprised you're investing in a new bike! Have you decided on a specific type or brand yet?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000062-0002</t>
+  </si>
+  <si>
+    <t>I'm thrilled to see more young people engaging in politics.</t>
+  </si>
+  <si>
+    <t>It's great to see new voices and ideas. How do you think young people can make a difference?</t>
+  </si>
+  <si>
+    <t>It's encouraging to see young voices being heard. How can we continue to engage more people?</t>
+  </si>
+  <si>
+    <t>It's great to see the younger generation taking an interest in politics.</t>
+  </si>
+  <si>
+    <t>Yes, it's inspiring to see a more youthful interest in politics.</t>
+  </si>
+  <si>
+    <t>Yes, it's inspiring to witness their dedication. How do you think they can make a difference?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0002</t>
@@ -644,67 +644,67 @@
     <t>Yes, it's fascinating how much we're learning about the universe. It's so exciting!</t>
   </si>
   <si>
-    <t>SFTANNO-000108-0002</t>
-  </si>
-  <si>
-    <t>Does it always have to be so muggy and humid after a rain like this?</t>
-  </si>
-  <si>
-    <t>It's infuriating how every time it rains, the humidity level skyrockets.</t>
-  </si>
-  <si>
-    <t>It's so frustrating when the weather feels unbearable for days on end.</t>
-  </si>
-  <si>
-    <t>And don't even get me started on how hard it is to dry our clothes after a rain like this.</t>
-  </si>
-  <si>
-    <t>It's frustrating how long it takes for the weather to go back to normal.</t>
-  </si>
-  <si>
-    <t>And don't even get me started on the mold and mildew that can grow in this weather.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000147-0002</t>
-  </si>
-  <si>
-    <t>Yes, I switched to a new service and they've been fantastic so far.</t>
-  </si>
-  <si>
-    <t>I'm glad you found a good one, but it's frustrating that you had to go through the hassle of finding the right one.</t>
-  </si>
-  <si>
-    <t>It's frustrating that you had to go through all that hassle, but I'm glad you found a new service that works for you.</t>
-  </si>
-  <si>
-    <t>It's ridiculous that you had to go through all that trouble to find a good service.</t>
-  </si>
-  <si>
-    <t>I had a bad experience with a cleaner once too, they left a mess behind and didn't show up for a week.</t>
-  </si>
-  <si>
-    <t>I can't stand when cleaners are unprofessional, it's important to hold them accountable.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000065-0002</t>
-  </si>
-  <si>
-    <t>I fear that our votes won't make a real difference.</t>
-  </si>
-  <si>
-    <t>It's infuriating that our voices might not be heard, but we must keep fighting for change.</t>
-  </si>
-  <si>
-    <t>It's frustrating that some people dismiss the importance of voting.</t>
-  </si>
-  <si>
-    <t>It's maddening that some people think their vote won't matter.</t>
-  </si>
-  <si>
-    <t>It's infuriating that people don't see the power in their vote.</t>
-  </si>
-  <si>
-    <t>It's infuriating that some people dismiss the importance of voting.</t>
+    <t>SFTANNO-000124-0002</t>
+  </si>
+  <si>
+    <t>I bought a durian once, but the smell was unbearable.</t>
+  </si>
+  <si>
+    <t>I don't think I could handle the smell, it sounds awful.</t>
+  </si>
+  <si>
+    <t>I'm afraid to try it now.</t>
+  </si>
+  <si>
+    <t>I'm a little scared to try it now, thanks for the warning.</t>
+  </si>
+  <si>
+    <t>I'm a bit afraid to try it now, but I'm willing to give it a chance sometime in the future.</t>
+  </si>
+  <si>
+    <t>I'm too scared to try it, I don't want to risk the smell.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000028-0002</t>
+  </si>
+  <si>
+    <t>I'm planning to have a heart-to-heart conversation with them soon.</t>
+  </si>
+  <si>
+    <t>I'm genuinely surprised to hear this. It shows a willingness to make things right.</t>
+  </si>
+  <si>
+    <t>It's surprising to see how much progress you're willing to make. Keep it up!</t>
+  </si>
+  <si>
+    <t>It's amazing how a simple conversation can have a profound impact on our relationships.</t>
+  </si>
+  <si>
+    <t>I'm surprised, but it's a wonderful idea. I hope it brings you closer.</t>
+  </si>
+  <si>
+    <t>I'm surprised to hear that. I hope it brings you closer.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000194-0002</t>
+  </si>
+  <si>
+    <t>I'm worried about going too trendy and looking outdated in a few years.</t>
+  </si>
+  <si>
+    <t>It's always good to balance trendy pieces with more timeless ones. What kind of furniture are you thinking of getting?</t>
+  </si>
+  <si>
+    <t>Maybe try incorporating some classic pieces like a velvet armchair or a brass lamp?</t>
+  </si>
+  <si>
+    <t>Timeless pieces can be mixed with trendy items to create a unique look.</t>
+  </si>
+  <si>
+    <t>I suggest investing in some timeless pieces and adding trendy accents that can be easily swapped out.</t>
+  </si>
+  <si>
+    <t>Maybe consider timeless pieces and then add trendy accents to keep things fresh.</t>
   </si>
   <si>
     <t>SFTANNO-000066-0002</t>
@@ -728,67 +728,67 @@
     <t>It's heartbreaking to think about how many people will be affected by this.</t>
   </si>
   <si>
-    <t>SFTANNO-000097-0002</t>
-  </si>
-  <si>
-    <t>I just saw a celebrity on the train!</t>
-  </si>
-  <si>
-    <t>I don't know if I would have the courage to talk to them, but that must have been exciting.</t>
-  </si>
-  <si>
-    <t>Oh my gosh, I would have freaked out if I had seen them. I'm not sure I could handle that.</t>
-  </si>
-  <si>
-    <t>But also kind of intimidating, I hope they don't mind us staring at them.</t>
-  </si>
-  <si>
-    <t>I would be terrified if I saw a celebrity on the train, they must get so much attention.</t>
-  </si>
-  <si>
-    <t>I hope they don't recognize me and cause a scene.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000112-0002</t>
-  </si>
-  <si>
-    <t>Yes, please, and thanks for your help.</t>
-  </si>
-  <si>
-    <t>But remember, it's important to read the policy thoroughly to avoid any surprises or hidden costs.</t>
-  </si>
-  <si>
-    <t>But please remember, even with insurance, healthcare can be expensive. Make sure to plan and budget accordingly.</t>
-  </si>
-  <si>
-    <t>Just remember, it's important to research thoroughly and choose the right plan for your needs.</t>
-  </si>
-  <si>
-    <t>Remember, healthcare is important, and I hope you're able to find a plan that works for you.</t>
-  </si>
-  <si>
-    <t>Just make sure to do your research and read the fine print before choosing a plan.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000104-0002</t>
-  </si>
-  <si>
-    <t>I haven't, but I'm definitely looking into it.</t>
-  </si>
-  <si>
-    <t>I'm sorry you had to go through that experience, but I'm glad you're taking steps to protect yourself and find a more welcoming community.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that we have to actively seek out communities that prioritize respect and inclusivity, but it's important to prioritize our own well-being.</t>
-  </si>
-  <si>
-    <t>It's sad that online spaces can be so toxic sometimes. But there are still many wonderful communities out there.</t>
-  </si>
-  <si>
-    <t>It's sad that such behavior exists, but we can make a difference by supporting and creating positive spaces.</t>
-  </si>
-  <si>
-    <t>It's so sad that there are people who use online spaces to spread negativity and hate.</t>
+    <t>SFTANNO-000122-0002</t>
+  </si>
+  <si>
+    <t>Did you know that some plants have developed the ability to repel insects through their scent?</t>
+  </si>
+  <si>
+    <t>It's so frustrating that some insects can cause so much damage to plants, especially when we work so hard to care for them.</t>
+  </si>
+  <si>
+    <t>It's so frustrating when pests damage plants, have you had any issues with that?</t>
+  </si>
+  <si>
+    <t>It's frustrating how some plants require constant maintenance, like deadheading, to keep them looking their best.</t>
+  </si>
+  <si>
+    <t>I wish I had known that earlier, my plants are constantly under attack from pesky insects.</t>
+  </si>
+  <si>
+    <t>It's a shame that some people choose to harm plants instead of appreciating their unique qualities.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000047-0002</t>
+  </si>
+  <si>
+    <t>I'm open to trying anything new! Do you have any recommendations?</t>
+  </si>
+  <si>
+    <t>But be careful, some Thai restaurants can be too loud and chaotic. I had a terrible experience at one place.</t>
+  </si>
+  <si>
+    <t>Vietnamese food is so much better than Thai food. I can't believe you're even considering Thai food over Vietnamese.</t>
+  </si>
+  <si>
+    <t>It's frustrating that people often overlook Asian cuisine when it has so much to offer.</t>
+  </si>
+  <si>
+    <t>Just be careful, Indian cuisine has a reputation for being too spicy. Some dishes can be modified to be less spicy though.</t>
+  </si>
+  <si>
+    <t>However, I'm not a fan of sushi, so I'd suggest trying something else like tempura or udon noodles.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000150-0002</t>
+  </si>
+  <si>
+    <t>I feel like all the tutorials online are too advanced for me!</t>
+  </si>
+  <si>
+    <t>Just take a deep breath, and remember that everyone starts somewhere.</t>
+  </si>
+  <si>
+    <t>Let's try searching for tutorials specifically for beginners. I'm sure we can find something that works for us.</t>
+  </si>
+  <si>
+    <t>Have you tried looking for tutorials that use simple materials and steps?</t>
+  </si>
+  <si>
+    <t>I'm so angry at how confusing some tutorials can be, but don't give up, we can find a beginner-friendly tutorial together.</t>
+  </si>
+  <si>
+    <t>It's ridiculous that tutorials can be so inaccessible.</t>
   </si>
   <si>
     <t>SFTANNO-000006-0002</t>
@@ -833,130 +833,130 @@
     <t>I'm interested in learning more about it. Do you have any sources you recommend?</t>
   </si>
   <si>
-    <t>SFTANNO-000110-0002</t>
-  </si>
-  <si>
-    <t>Yeah, I watched a tornado make landfall and destroy an entire neighborhood. It was heartbreaking.</t>
-  </si>
-  <si>
-    <t>It's so sad that something as natural as a tornado can cause so much destruction and loss.</t>
-  </si>
-  <si>
-    <t>It's so devastating to see the destruction and loss of life that tornadoes can cause.</t>
-  </si>
-  <si>
-    <t>I'm so sorry you had to go through that. It's really heartbreaking.</t>
-  </si>
-  <si>
-    <t>It's so sad that tornadoes can cause so much destruction and heartache.</t>
-  </si>
-  <si>
-    <t>It's so sad to think about the destruction and loss of life that tornadoes can cause.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000063-0002</t>
-  </si>
-  <si>
-    <t>I'm happy to see more political discussions in our community.</t>
-  </si>
-  <si>
-    <t>It's about time. The apathy in the past was infuriating.</t>
-  </si>
-  <si>
-    <t>It's fantastic, but it's frustrating when some refuse to engage.</t>
-  </si>
-  <si>
-    <t>But, we need to ensure that these discussions are respectful and not divisive.</t>
-  </si>
-  <si>
-    <t>It's great, but we need to address the polarization. It's dividing us.</t>
-  </si>
-  <si>
-    <t>While it's good, the polarization is disheartening. We need more unity.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000003-0002</t>
-  </si>
-  <si>
-    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
-  </si>
-  <si>
-    <t>I'm surprised that you've been using the same lens for so long, that's impressive!</t>
-  </si>
-  <si>
-    <t>It's surprising how much hygiene can matter when using someone else's equipment.</t>
-  </si>
-  <si>
-    <t>I'm surprised you wouldn't consider renting a lens, it can be a cost-effective way to try out different lenses.</t>
-  </si>
-  <si>
-    <t>I'm surprised you'd consider using someone else's lens.</t>
-  </si>
-  <si>
-    <t>I'm surprised you haven't tried renting a lens before.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000172-0002</t>
-  </si>
-  <si>
-    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
-  </si>
-  <si>
-    <t>I'm surprised by their lack of openness. Have you considered sharing resources with them?</t>
-  </si>
-  <si>
-    <t>It's surprising how resistant some can be to new ideas. How do you approach those who dismiss mindfulness?</t>
-  </si>
-  <si>
-    <t>It's surprising how little some people are willing to listen. Have you considered sharing your experiences on social media?</t>
-  </si>
-  <si>
-    <t>It's surprising that they don't want to explore the benefits. How do you cope with their skepticism?</t>
-  </si>
-  <si>
-    <t>It's surprising how difficult it can be to change someone's perspective.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000087-0002</t>
-  </si>
-  <si>
-    <t>Can you believe the other team won with that cheap shot?</t>
-  </si>
-  <si>
-    <t>But don't worry, we'll come back stronger next time!</t>
-  </si>
-  <si>
-    <t>But we still won the game, so it doesn't really matter in the end.</t>
-  </si>
-  <si>
-    <t>I'm so happy we won the game despite all the unfair calls. It was such a great win.</t>
-  </si>
-  <si>
-    <t>But on a positive note, our team played really well, despite the loss.</t>
-  </si>
-  <si>
-    <t>But hey, we still have a chance to make it to the finals.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000133-0002</t>
-  </si>
-  <si>
-    <t>I recently learned about a beautiful hiking trail in Norway that I'm dying to see.</t>
-  </si>
-  <si>
-    <t>It's frustrating that I haven't had the chance to explore more of the world yet.</t>
-  </si>
-  <si>
-    <t>It's so frustrating that there are so many incredible places in the world to see, and we only have so much time to see them all.</t>
-  </si>
-  <si>
-    <t>It's frustrating that I haven't had the chance to travel as much as I want to.</t>
-  </si>
-  <si>
-    <t>It's frustrating when we discover something amazing but can't immediately go see it for ourselves.</t>
-  </si>
-  <si>
-    <t>It's frustrating that some of the most beautiful places in the world are only accessible to those who can afford to travel.</t>
+    <t>SFTANNO-000128-0002</t>
+  </si>
+  <si>
+    <t>I tried growing herbs inside, but it didn't work out.</t>
+  </si>
+  <si>
+    <t>It's tough when our plants don't thrive. But don't give up! We'll figure out a way to make it work.</t>
+  </si>
+  <si>
+    <t>I'm sorry to hear that. It's tough when our plants don't thrive. But don't give up, keep experimenting and trying new things!</t>
+  </si>
+  <si>
+    <t>It's tough when things don't work out, but don't give up! There are so many different methods to try.</t>
+  </si>
+  <si>
+    <t>It's hard to see our plants not thrive, but don't give up. We'll find what works for you.</t>
+  </si>
+  <si>
+    <t>It's tough when we can't get our plants to thrive, but don't give up!</t>
+  </si>
+  <si>
+    <t>SFTANNO-000090-0002</t>
+  </si>
+  <si>
+    <t>I think we can celebrate when our team shows good sportsmanship and talk about how it makes everyone feel great.</t>
+  </si>
+  <si>
+    <t>It's sad that good sportsmanship isn't always the norm, but we can work towards changing that.</t>
+  </si>
+  <si>
+    <t>It's too bad that not all teams prioritize sportsmanship like yours, but we can still celebrate our own success and continue to set a good example.</t>
+  </si>
+  <si>
+    <t>It's too bad that not all teams share that same value, but we can still promote it in our own team.</t>
+  </si>
+  <si>
+    <t>It's too bad that some teams don't see the value in good sportsmanship, but we can lead by example and make it a priority.</t>
+  </si>
+  <si>
+    <t>It's unfortunate that some teams don't prioritize good sportsmanship, but we can focus on our own team and make sure we're doing our best.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000135-0002</t>
+  </si>
+  <si>
+    <t>I did a river rafting trip once, but the water was so dirty.</t>
+  </si>
+  <si>
+    <t>River rafting can be a thrilling adventure, but make sure you choose a reputable company and do your research beforehand.</t>
+  </si>
+  <si>
+    <t>It's important to prioritize safety and cleanliness when it comes to adventure activities.</t>
+  </si>
+  <si>
+    <t>I can understand why you wouldn't want to raft in dirty water.</t>
+  </si>
+  <si>
+    <t>It's important to do your research and choose a reputable company that takes safety and cleanliness seriously.</t>
+  </si>
+  <si>
+    <t>It's important to do research on the cleanliness of the river and the safety of the rafting company.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000102-0002</t>
+  </si>
+  <si>
+    <t>The new Pokemon game is such a cash grab. They're releasing the same version with only minor updates.</t>
+  </si>
+  <si>
+    <t>It's infuriating, they should be focusing on making better games.</t>
+  </si>
+  <si>
+    <t>It feels like they're not even trying anymore.</t>
+  </si>
+  <si>
+    <t>They're exploiting their loyal fanbase, it's maddening.</t>
+  </si>
+  <si>
+    <t>It's frustrating when companies rely on their brand instead of innovation.</t>
+  </si>
+  <si>
+    <t>It's just a ploy to make more money, it's not fair to the fans.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000183-0002</t>
+  </si>
+  <si>
+    <t>The Assyrians had a reputation for extreme cruelty towards those they conquered.</t>
+  </si>
+  <si>
+    <t>It's scary to think about how much power and influence they had in the region.</t>
+  </si>
+  <si>
+    <t>And it's scary to think about the fear they instilled in their enemies with their ruthless tactics.</t>
+  </si>
+  <si>
+    <t>It's frightening to think about how far they would go to maintain their power.</t>
+  </si>
+  <si>
+    <t>It's scary to think about how they used terror tactics to conquer other civilizations.</t>
+  </si>
+  <si>
+    <t>It's scary to think about the power that the Assyrians had and how they used it to control others.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000043-0002</t>
+  </si>
+  <si>
+    <t>I was skeptical at first, but I tried incorporating avocado in my breakfast, and it was delicious!</t>
+  </si>
+  <si>
+    <t>It's frustrating how the diet industry can make us feel like we're not good enough, but we have the power to make healthy choices for ourselves.</t>
+  </si>
+  <si>
+    <t>It's frustrating how the diet industry often promotes quick fixes instead of sustainable healthy habits.</t>
+  </si>
+  <si>
+    <t>I'm so surprised to hear that you liked it! I'm so disappointed that I didn't get to try it with you.</t>
+  </si>
+  <si>
+    <t>It's frustrating that healthy food options aren't always marketed as tasty, but it's worth experimenting to find healthy options that you enjoy.</t>
+  </si>
+  <si>
+    <t>It's frustrating how many fad diets out there are just marketing gimmicks that prey on people's insecurities.</t>
   </si>
   <si>
     <t>SFTANNO-000011-0002</t>
@@ -1007,55 +1007,22 @@
     <t>Neutral</t>
   </si>
   <si>
+    <t>Disgust</t>
+  </si>
+  <si>
+    <t>Sadness</t>
+  </si>
+  <si>
+    <t>Happiness</t>
+  </si>
+  <si>
+    <t>Surprise</t>
+  </si>
+  <si>
     <t>Fear</t>
   </si>
   <si>
-    <t>Sadness</t>
-  </si>
-  <si>
-    <t>Happiness</t>
-  </si>
-  <si>
-    <t>Surprise</t>
-  </si>
-  <si>
-    <t>Al ser texto es dificil saber la emoción. Ayuda un poco el hecho de que ciertas palabras aparezcan. El uso de signos de puntuación también podría ayudar</t>
-  </si>
-  <si>
-    <t>En el modelo 3 hay dos emociones: felicidad y miedo. En las otras me decanto por el mideo porque no expresa tanta felicidad.</t>
-  </si>
-  <si>
-    <t>Disgust</t>
-  </si>
-  <si>
     <t>Anger</t>
-  </si>
-  <si>
-    <t>falta contexto</t>
-  </si>
-  <si>
-    <t>La emoción del modelo 2 no me parece incluida en la lista. Es como si fuera ironía y a la vez optimismo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En el modelo 5 comento ira, pero es más por el tono serio de la frase. </t>
-  </si>
-  <si>
-    <t>Ira por el tono serio. Muy diferente a las respuestas de los modelos 4 y 5</t>
-  </si>
-  <si>
-    <t>Varias emociones a la vez. Me decanto por neutral</t>
-  </si>
-  <si>
-    <t>Hay varias emociones. Dificil elección</t>
-  </si>
-  <si>
-    <t>Hay dos emociones. Una de tristeza al principio y la otra optimista. No creo que Neutral sea la solución</t>
-  </si>
-  <si>
-    <t>La respuesta del modelo 2 no es congruente</t>
-  </si>
-  <si>
-    <t>falta contexto. Son raras las respuestas del 3 y 4</t>
   </si>
 </sst>
 </file>
@@ -1074,6 +1041,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1111,16 +1079,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1425,14 +1390,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N46"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="14" width="28.33203125" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="2" max="2" width="28.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.1640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="28.1640625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1476,7 +1451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -1496,19 +1471,19 @@
         <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -1516,9 +1491,8 @@
       <c r="M2" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1526,41 +1500,40 @@
         <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1568,7 +1541,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>29</v>
@@ -1600,11 +1573,8 @@
       <c r="M4" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1612,7 +1582,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>36</v>
@@ -1624,13 +1594,13 @@
         <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>39</v>
@@ -1644,11 +1614,8 @@
       <c r="M5" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1656,13 +1623,13 @@
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>44</v>
@@ -1680,7 +1647,7 @@
         <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>47</v>
@@ -1688,9 +1655,8 @@
       <c r="M6" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1698,41 +1664,40 @@
         <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>54</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1740,41 +1705,40 @@
         <v>56</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>60</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1782,41 +1746,40 @@
         <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1824,7 +1787,7 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>71</v>
@@ -1836,13 +1799,13 @@
         <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>74</v>
@@ -1856,9 +1819,8 @@
       <c r="M10" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1866,41 +1828,40 @@
         <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1908,43 +1869,40 @@
         <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="80" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1952,43 +1910,40 @@
         <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>94</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>96</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1996,25 +1951,25 @@
         <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>102</v>
@@ -2026,13 +1981,10 @@
         <v>103</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -2046,35 +1998,34 @@
         <v>106</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>109</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>110</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -2082,41 +2033,40 @@
         <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>114</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>115</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>116</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>117</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -2124,31 +2074,31 @@
         <v>119</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>121</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>122</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>123</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>124</v>
@@ -2156,11 +2106,8 @@
       <c r="M17" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -2168,43 +2115,40 @@
         <v>126</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>127</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>128</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>129</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>130</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -2212,41 +2156,40 @@
         <v>133</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>134</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>136</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>137</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>138</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -2254,41 +2197,40 @@
         <v>140</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>142</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>143</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>144</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>145</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -2296,41 +2238,40 @@
         <v>147</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>151</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>152</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -2338,43 +2279,40 @@
         <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>156</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>158</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>159</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>160</v>
       </c>
@@ -2382,41 +2320,40 @@
         <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>162</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>163</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>165</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>166</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>167</v>
       </c>
@@ -2424,41 +2361,40 @@
         <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>171</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>173</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>174</v>
       </c>
@@ -2466,43 +2402,40 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>177</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>179</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>180</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>181</v>
       </c>
@@ -2510,41 +2443,40 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>183</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>184</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>186</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>187</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>188</v>
       </c>
@@ -2552,19 +2484,19 @@
         <v>189</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>190</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>191</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>192</v>
@@ -2576,7 +2508,7 @@
         <v>193</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>194</v>
@@ -2584,9 +2516,8 @@
       <c r="M27" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="N27" s="2"/>
-    </row>
-    <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>195</v>
       </c>
@@ -2594,7 +2525,7 @@
         <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>197</v>
@@ -2612,7 +2543,7 @@
         <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>200</v>
@@ -2626,9 +2557,8 @@
       <c r="M28" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>202</v>
       </c>
@@ -2636,41 +2566,40 @@
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>205</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>206</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>207</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>208</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="N29" s="2"/>
-    </row>
-    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>209</v>
       </c>
@@ -2678,41 +2607,40 @@
         <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>212</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>213</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>214</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>215</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>216</v>
       </c>
@@ -2720,41 +2648,40 @@
         <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>218</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>219</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>221</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>222</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>223</v>
       </c>
@@ -2762,41 +2689,40 @@
         <v>224</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>226</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>227</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>228</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>229</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>230</v>
       </c>
@@ -2804,7 +2730,7 @@
         <v>231</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>232</v>
@@ -2816,29 +2742,28 @@
         <v>233</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>234</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>235</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>236</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>237</v>
       </c>
@@ -2846,7 +2771,7 @@
         <v>238</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>239</v>
@@ -2878,9 +2803,8 @@
       <c r="M34" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>244</v>
       </c>
@@ -2900,13 +2824,13 @@
         <v>247</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>248</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>249</v>
@@ -2918,11 +2842,10 @@
         <v>250</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="N35" s="2"/>
-    </row>
-    <row r="36" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>251</v>
       </c>
@@ -2930,41 +2853,40 @@
         <v>252</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>253</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>255</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>256</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>257</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>258</v>
       </c>
@@ -2972,41 +2894,40 @@
         <v>259</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>260</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>261</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>262</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>263</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>264</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>265</v>
       </c>
@@ -3026,19 +2947,19 @@
         <v>268</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>269</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>270</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>271</v>
@@ -3046,9 +2967,8 @@
       <c r="M38" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>272</v>
       </c>
@@ -3062,7 +2982,7 @@
         <v>274</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>275</v>
@@ -3088,9 +3008,8 @@
       <c r="M39" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="N39" s="2"/>
-    </row>
-    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>279</v>
       </c>
@@ -3098,31 +3017,31 @@
         <v>280</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>281</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>282</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>283</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>284</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>285</v>
@@ -3130,9 +3049,8 @@
       <c r="M40" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="N40" s="2"/>
-    </row>
-    <row r="41" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>286</v>
       </c>
@@ -3140,41 +3058,40 @@
         <v>287</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>288</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>289</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>291</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>292</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="N41" s="2"/>
-    </row>
-    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>293</v>
       </c>
@@ -3182,41 +3099,40 @@
         <v>294</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>295</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>297</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>298</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>299</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="N42" s="2"/>
-    </row>
-    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>300</v>
       </c>
@@ -3224,41 +3140,40 @@
         <v>301</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>302</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>303</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>304</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>305</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>306</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="N43" s="2"/>
-    </row>
-    <row r="44" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>307</v>
       </c>
@@ -3272,37 +3187,34 @@
         <v>309</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>310</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>311</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>312</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>313</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>314</v>
       </c>
@@ -3310,13 +3222,13 @@
         <v>315</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>316</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>317</v>
@@ -3342,11 +3254,8 @@
       <c r="M45" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>321</v>
       </c>
@@ -3354,25 +3263,25 @@
         <v>322</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>323</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>324</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>325</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>326</v>
@@ -3384,13 +3293,12 @@
         <v>327</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>330</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C46 E2:E46 G2:G46 I2:I46 K2:K46 M2:M46" xr:uid="{23AE58DB-43D3-4610-B7CF-96C69284197E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C46 E2:E46 G2:G46 I2:I46 K2:K46 M2:M46" xr:uid="{2A8B2AD2-5ED7-46F4-9531-422CF7F7D578}">
       <formula1>"Anger,Disgust,Fear,Happiness,Sadness,Surprise,Neutral"</formula1>
     </dataValidation>
   </dataValidations>
